--- a/mca_sem/static/TR/MCA_4_TR_FORMATE.xlsx
+++ b/mca_sem/static/TR/MCA_4_TR_FORMATE.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="57">
   <si>
     <t xml:space="preserve"> Purnea University, Purnia, Bihar</t>
   </si>
@@ -65,7 +65,10 @@
     <t xml:space="preserve">4MCACCC1 </t>
   </si>
   <si>
-    <t>Agreegate(7+10+13+16+19+22+25+26)</t>
+    <t>Grand Total(16+19+22+25+28+29)</t>
+  </si>
+  <si>
+    <t>Agreegate(6+9+12+30)</t>
   </si>
   <si>
     <t>Result</t>
@@ -140,16 +143,16 @@
     <t>2218M240002</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>No. of Candidate:  01</t>
+    <t>1ˢᵗ Class</t>
+  </si>
+  <si>
+    <t>No. of Students:  01</t>
   </si>
   <si>
     <t>First Class with Distinction:</t>
   </si>
   <si>
-    <t>1st Class:</t>
+    <t>1st Class: 01</t>
   </si>
   <si>
     <t>Promoted:</t>
@@ -188,7 +191,7 @@
     <t xml:space="preserve">Qualified: </t>
   </si>
   <si>
-    <t>Pass: 01</t>
+    <t>Pass:</t>
   </si>
   <si>
     <t>Disqualified:</t>
@@ -262,6 +265,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="10"/>
       <name val="Times New Roman"/>
@@ -274,11 +282,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <name val="Times New Roman"/>
@@ -289,6 +292,14 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -362,14 +373,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -749,6 +752,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -796,21 +814,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -863,43 +866,43 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
@@ -993,7 +996,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1045,16 +1048,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1074,34 +1074,29 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="17" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1170,16 +1165,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>149225</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>231140</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>323215</xdr:rowOff>
+      <xdr:rowOff>264160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>223309</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>305224</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>418465</xdr:rowOff>
+      <xdr:rowOff>359410</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1196,7 +1191,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10594340" y="323215"/>
+          <a:off x="8683625" y="264160"/>
           <a:ext cx="1189990" cy="1190625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1496,19 +1491,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AL24"/>
+  <dimension ref="A1:AM26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="13.4259259259259" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18.1388888888889" style="4" customWidth="1"/>
-    <col min="3" max="3" width="21.5740740740741" style="4" customWidth="1"/>
-    <col min="4" max="4" width="5.62962962962963" style="4" customWidth="1"/>
+    <col min="1" max="1" width="9.61111111111111" style="4" customWidth="1"/>
+    <col min="2" max="2" width="12.6018518518519" style="4" customWidth="1"/>
+    <col min="3" max="3" width="16.9166666666667" style="4" customWidth="1"/>
+    <col min="4" max="4" width="10.7777777777778" style="4" customWidth="1"/>
     <col min="5" max="5" width="5.46296296296296" style="4" customWidth="1"/>
     <col min="6" max="6" width="5.2962962962963" style="4" customWidth="1"/>
-    <col min="7" max="7" width="6.12037037037037" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9.77777777777778" style="4" customWidth="1"/>
     <col min="8" max="8" width="6.4537037037037" style="4" customWidth="1"/>
     <col min="9" max="9" width="6.2962962962963" style="4" customWidth="1"/>
-    <col min="10" max="10" width="6.46296296296296" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9.4537037037037" style="4" customWidth="1"/>
     <col min="11" max="11" width="6.4537037037037" style="4" customWidth="1"/>
     <col min="12" max="12" width="6.2962962962963" style="4" customWidth="1"/>
     <col min="13" max="13" width="12.1388888888889" style="4" customWidth="1"/>
@@ -1523,13 +1518,14 @@
     <col min="26" max="27" width="5.71296296296296" style="4" customWidth="1"/>
     <col min="28" max="28" width="6.28703703703704" style="4" customWidth="1"/>
     <col min="29" max="29" width="18" style="4" customWidth="1"/>
-    <col min="30" max="30" width="9.13888888888889" style="4" customWidth="1"/>
-    <col min="31" max="31" width="10.712962962963" style="4" customWidth="1"/>
-    <col min="32" max="32" width="27.4259259259259" style="4" customWidth="1"/>
-    <col min="33" max="16384" width="9.13888888888889" style="4"/>
+    <col min="30" max="30" width="10.4444444444444" style="4" customWidth="1"/>
+    <col min="31" max="31" width="9.13888888888889" style="4" customWidth="1"/>
+    <col min="32" max="32" width="10.712962962963" style="4" customWidth="1"/>
+    <col min="33" max="33" width="16.4166666666667" style="4" customWidth="1"/>
+    <col min="34" max="16384" width="9.13888888888889" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="86.25" customHeight="1" spans="1:32">
+    <row r="1" ht="86.25" customHeight="1" spans="1:33">
       <c r="A1" s="5"/>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1562,8 +1558,9 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
       <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
     </row>
-    <row r="2" ht="68.25" customHeight="1" spans="1:32">
+    <row r="2" ht="68.25" customHeight="1" spans="1:33">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -1598,8 +1595,9 @@
       <c r="AD2" s="6"/>
       <c r="AE2" s="6"/>
       <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
     </row>
-    <row r="3" ht="32.4" spans="1:32">
+    <row r="3" ht="32.4" spans="1:33">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
@@ -1634,8 +1632,9 @@
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
     </row>
-    <row r="4" ht="32.4" spans="1:32">
+    <row r="4" ht="32.4" spans="1:33">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1656,22 +1655,23 @@
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
-      <c r="U4" s="34" t="s">
+      <c r="U4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-      <c r="X4" s="34"/>
-      <c r="Y4" s="34"/>
-      <c r="Z4" s="34"/>
-      <c r="AA4" s="34"/>
-      <c r="AB4" s="34"/>
-      <c r="AC4" s="34"/>
-      <c r="AD4" s="34"/>
-      <c r="AE4" s="34"/>
-      <c r="AF4" s="34"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="33"/>
+      <c r="Y4" s="33"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="33"/>
+      <c r="AB4" s="33"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="33"/>
+      <c r="AE4" s="33"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="33"/>
     </row>
-    <row r="5" ht="22.8" spans="1:32">
+    <row r="5" ht="22.8" spans="1:33">
       <c r="A5" s="5"/>
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
@@ -1692,22 +1692,23 @@
       <c r="R5" s="5"/>
       <c r="S5" s="5"/>
       <c r="T5" s="5"/>
-      <c r="U5" s="34" t="s">
+      <c r="U5" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="34"/>
-      <c r="Y5" s="34"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34"/>
-      <c r="AD5" s="34"/>
-      <c r="AE5" s="34"/>
-      <c r="AF5" s="34"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
+      <c r="AE5" s="33"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="33"/>
     </row>
-    <row r="6" ht="26.25" customHeight="1" spans="1:32">
+    <row r="6" ht="26.25" customHeight="1" spans="1:33">
       <c r="A6" s="8" t="s">
         <v>4</v>
       </c>
@@ -1730,22 +1731,23 @@
       <c r="R6" s="5"/>
       <c r="S6" s="5"/>
       <c r="T6" s="5"/>
-      <c r="U6" s="35" t="s">
+      <c r="U6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="35"/>
-      <c r="W6" s="35"/>
-      <c r="X6" s="35"/>
-      <c r="Y6" s="35"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="35"/>
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="34"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="34"/>
+      <c r="AA6" s="34"/>
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="34"/>
+      <c r="AE6" s="34"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="34"/>
     </row>
-    <row r="7" ht="26.25" customHeight="1" spans="1:32">
+    <row r="7" ht="26.25" customHeight="1" spans="1:33">
       <c r="A7" s="9"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
@@ -1759,185 +1761,190 @@
       <c r="K7" s="12"/>
       <c r="L7" s="13"/>
       <c r="M7" s="10"/>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="O7" s="29"/>
-      <c r="P7" s="29"/>
-      <c r="Q7" s="29" t="s">
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29" t="s">
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="29"/>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29" t="s">
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="X7" s="29"/>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29" t="s">
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="AA7" s="29"/>
-      <c r="AB7" s="29"/>
-      <c r="AC7" s="29" t="s">
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AD7" s="36" t="s">
+      <c r="AD7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="AE7" s="14" t="s">
+      <c r="AE7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="AF7" s="37" t="s">
+      <c r="AF7" s="14" t="s">
         <v>14</v>
       </c>
+      <c r="AG7" s="41" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="8" ht="55" customHeight="1" spans="1:32">
+    <row r="8" ht="55" customHeight="1" spans="1:33">
       <c r="A8" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="17"/>
       <c r="G8" s="15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H8" s="16"/>
       <c r="I8" s="17"/>
       <c r="J8" s="16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K8" s="16"/>
       <c r="L8" s="17"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30" t="s">
+      <c r="M8" s="28"/>
+      <c r="N8" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="30"/>
-      <c r="T8" s="30" t="s">
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30" t="s">
+      <c r="R8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="30" t="s">
+      <c r="U8" s="29"/>
+      <c r="V8" s="29"/>
+      <c r="W8" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="AA8" s="30"/>
-      <c r="AB8" s="30"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29"/>
       <c r="AC8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD8" s="38"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="37"/>
+        <v>27</v>
+      </c>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="35"/>
+      <c r="AF8" s="14"/>
+      <c r="AG8" s="41"/>
     </row>
-    <row r="9" ht="219" customHeight="1" spans="1:32">
+    <row r="9" ht="219" customHeight="1" spans="1:33">
       <c r="A9" s="14"/>
       <c r="B9" s="14"/>
       <c r="C9" s="14"/>
       <c r="D9" s="14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="H9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="H9" s="14" t="s">
+      <c r="I9" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>28</v>
-      </c>
       <c r="L9" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="M9" s="28"/>
+      <c r="N9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="P9" s="31" t="s">
+      <c r="O9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="Q9" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="R9" s="31" t="s">
+      <c r="P9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="S9" s="31" t="s">
+      <c r="R9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="T9" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="U9" s="31" t="s">
+      <c r="S9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="T9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="V9" s="31" t="s">
+      <c r="U9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="W9" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="X9" s="31" t="s">
+      <c r="V9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="W9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="Y9" s="31" t="s">
+      <c r="X9" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="Z9" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="AA9" s="31" t="s">
+      <c r="Y9" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="AB9" s="31" t="s">
+      <c r="AA9" s="30" t="s">
         <v>32</v>
       </c>
+      <c r="AB9" s="30" t="s">
+        <v>33</v>
+      </c>
       <c r="AC9" s="14"/>
-      <c r="AD9" s="39"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="37"/>
+      <c r="AD9" s="19"/>
+      <c r="AE9" s="19"/>
+      <c r="AF9" s="14"/>
+      <c r="AG9" s="41"/>
     </row>
-    <row r="10" ht="33.75" customHeight="1" spans="1:32">
+    <row r="10" ht="33.75" customHeight="1" spans="1:33">
       <c r="A10" s="14"/>
       <c r="B10" s="14"/>
       <c r="C10" s="14"/>
@@ -1950,64 +1957,67 @@
       <c r="J10" s="18"/>
       <c r="K10" s="18"/>
       <c r="L10" s="18"/>
-      <c r="M10" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="N10" s="32">
+      <c r="M10" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="N10" s="31">
         <v>70</v>
       </c>
-      <c r="O10" s="32">
+      <c r="O10" s="31">
         <v>30</v>
       </c>
-      <c r="P10" s="32">
+      <c r="P10" s="31">
         <v>100</v>
       </c>
-      <c r="Q10" s="32">
+      <c r="Q10" s="31">
         <v>70</v>
       </c>
-      <c r="R10" s="32">
+      <c r="R10" s="31">
         <v>30</v>
       </c>
-      <c r="S10" s="32">
+      <c r="S10" s="31">
         <v>100</v>
       </c>
-      <c r="T10" s="32">
+      <c r="T10" s="31">
         <v>70</v>
       </c>
-      <c r="U10" s="32">
+      <c r="U10" s="31">
         <v>30</v>
       </c>
-      <c r="V10" s="32">
+      <c r="V10" s="31">
         <v>100</v>
       </c>
-      <c r="W10" s="32">
+      <c r="W10" s="31">
         <v>70</v>
       </c>
-      <c r="X10" s="32">
+      <c r="X10" s="31">
         <v>30</v>
       </c>
-      <c r="Y10" s="32">
+      <c r="Y10" s="31">
         <v>100</v>
       </c>
-      <c r="Z10" s="32">
+      <c r="Z10" s="31">
         <v>200</v>
       </c>
-      <c r="AA10" s="32">
+      <c r="AA10" s="31">
         <v>100</v>
       </c>
-      <c r="AB10" s="32">
+      <c r="AB10" s="31">
         <v>300</v>
       </c>
-      <c r="AC10" s="32">
+      <c r="AC10" s="31">
         <v>100</v>
       </c>
-      <c r="AD10" s="32">
+      <c r="AD10" s="31">
         <v>800</v>
       </c>
-      <c r="AE10" s="14"/>
-      <c r="AF10" s="37"/>
+      <c r="AE10" s="31">
+        <v>3200</v>
+      </c>
+      <c r="AF10" s="14"/>
+      <c r="AG10" s="41"/>
     </row>
-    <row r="11" ht="33" customHeight="1" spans="1:32">
+    <row r="11" ht="33" customHeight="1" spans="1:33">
       <c r="A11" s="14"/>
       <c r="B11" s="14"/>
       <c r="C11" s="14"/>
@@ -2020,54 +2030,55 @@
       <c r="J11" s="19"/>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
-      <c r="M11" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="N11" s="32">
+      <c r="M11" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="N11" s="31">
         <v>28</v>
       </c>
-      <c r="O11" s="32">
+      <c r="O11" s="31">
         <v>12</v>
       </c>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="32">
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31">
         <v>28</v>
       </c>
-      <c r="R11" s="32">
+      <c r="R11" s="31">
         <v>12</v>
       </c>
-      <c r="S11" s="32"/>
-      <c r="T11" s="32">
+      <c r="S11" s="31"/>
+      <c r="T11" s="31">
         <v>28</v>
       </c>
-      <c r="U11" s="32">
+      <c r="U11" s="31">
         <v>12</v>
       </c>
-      <c r="V11" s="32"/>
-      <c r="W11" s="32">
+      <c r="V11" s="31"/>
+      <c r="W11" s="31">
         <v>28</v>
       </c>
-      <c r="X11" s="32">
+      <c r="X11" s="31">
         <v>12</v>
       </c>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="32">
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="31">
         <v>80</v>
       </c>
-      <c r="AA11" s="32">
+      <c r="AA11" s="31">
         <v>40</v>
       </c>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="32">
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31">
         <v>40</v>
       </c>
-      <c r="AD11" s="32">
-        <v>320</v>
-      </c>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="37"/>
+      <c r="AD11" s="31">
+        <v>360</v>
+      </c>
+      <c r="AE11" s="36"/>
+      <c r="AF11" s="14"/>
+      <c r="AG11" s="41"/>
     </row>
-    <row r="12" ht="33.75" customHeight="1" spans="1:32">
+    <row r="12" ht="33.75" customHeight="1" spans="1:33">
       <c r="A12" s="20">
         <v>1</v>
       </c>
@@ -2077,111 +2088,134 @@
       <c r="C12" s="20">
         <v>3</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="20"/>
+      <c r="D12" s="20">
+        <v>4</v>
+      </c>
+      <c r="E12" s="20">
+        <v>5</v>
+      </c>
+      <c r="F12" s="20">
+        <v>6</v>
+      </c>
+      <c r="G12" s="20">
+        <v>7</v>
+      </c>
+      <c r="H12" s="20">
+        <v>8</v>
+      </c>
+      <c r="I12" s="20">
+        <v>9</v>
+      </c>
+      <c r="J12" s="20">
+        <v>10</v>
+      </c>
+      <c r="K12" s="20">
+        <v>11</v>
+      </c>
+      <c r="L12" s="20">
+        <v>12</v>
+      </c>
       <c r="M12" s="20">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N12" s="20">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O12" s="20">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="P12" s="20">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q12" s="20">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="R12" s="20">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="S12" s="20">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="T12" s="20">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="U12" s="20">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="V12" s="20">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="W12" s="20">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="X12" s="20">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Y12" s="20">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="Z12" s="20">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AA12" s="20">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AB12" s="20">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AC12" s="20">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AD12" s="20">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE12" s="20">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AF12" s="20">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="AG12" s="20">
+        <v>33</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="51" customHeight="1" spans="1:32">
+    <row r="13" s="1" customFormat="1" ht="51" customHeight="1" spans="1:33">
       <c r="A13" s="21">
         <v>121212</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="23">
+        <v>37</v>
+      </c>
+      <c r="D13" s="21">
         <v>121212</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="21">
         <v>800</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="21">
         <v>690</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="21">
         <v>121212</v>
       </c>
-      <c r="H13" s="23">
+      <c r="H13" s="21">
         <v>800</v>
       </c>
-      <c r="I13" s="23">
+      <c r="I13" s="21">
         <v>578</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="21">
         <v>121212</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="21">
         <v>800</v>
       </c>
-      <c r="L13" s="21"/>
+      <c r="L13" s="21">
+        <v>663</v>
+      </c>
       <c r="M13" s="21"/>
       <c r="N13" s="21">
         <v>63</v>
@@ -2231,315 +2265,272 @@
       <c r="AC13" s="21">
         <v>95</v>
       </c>
-      <c r="AD13" s="40">
+      <c r="AD13" s="21">
         <v>725</v>
       </c>
-      <c r="AE13" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF13" s="41"/>
+      <c r="AE13" s="37">
+        <v>2656</v>
+      </c>
+      <c r="AF13" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG13" s="42"/>
     </row>
-    <row r="14" spans="30:31">
-      <c r="AD14" s="42"/>
-      <c r="AE14" s="43"/>
+    <row r="14" spans="31:32">
+      <c r="AE14" s="38"/>
+      <c r="AF14" s="39"/>
     </row>
-    <row r="15" ht="15" customHeight="1" spans="30:31">
-      <c r="AD15" s="42"/>
-      <c r="AE15" s="43"/>
+    <row r="15" ht="15" customHeight="1" spans="31:32">
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="39"/>
     </row>
-    <row r="16" spans="30:31">
-      <c r="AD16" s="42"/>
-      <c r="AE16" s="43"/>
+    <row r="16" spans="31:32">
+      <c r="AE16" s="38"/>
+      <c r="AF16" s="39"/>
     </row>
-    <row r="17" spans="30:31">
-      <c r="AD17" s="42"/>
-      <c r="AE17" s="43"/>
+    <row r="17" spans="31:32">
+      <c r="AE17" s="38"/>
+      <c r="AF17" s="39"/>
     </row>
-    <row r="18" s="2" customFormat="1" ht="13.2" spans="1:38">
-      <c r="A18" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="24"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="26"/>
-      <c r="E18" s="26"/>
-      <c r="F18" s="26"/>
-      <c r="G18" s="26"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="26"/>
-      <c r="K18" s="26"/>
-      <c r="L18" s="26"/>
-      <c r="M18" s="26"/>
-      <c r="N18" s="26"/>
-      <c r="O18" s="26"/>
-      <c r="P18" s="26"/>
-      <c r="Q18" s="25"/>
-      <c r="R18" s="25"/>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-      <c r="V18" s="25"/>
-      <c r="W18" s="25"/>
-      <c r="X18" s="25"/>
-      <c r="Y18" s="25"/>
-      <c r="Z18" s="25"/>
-      <c r="AA18" s="25"/>
-      <c r="AB18" s="25"/>
-      <c r="AC18" s="25"/>
-      <c r="AD18" s="25"/>
-      <c r="AE18" s="25"/>
-      <c r="AF18" s="25"/>
-      <c r="AG18" s="25"/>
-      <c r="AH18" s="25"/>
+    <row r="18" s="2" customFormat="1" ht="13.2" spans="35:39">
       <c r="AI18" s="25"/>
-      <c r="AJ18" s="45"/>
-      <c r="AK18" s="25"/>
-      <c r="AL18" s="26"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="43"/>
+      <c r="AL18" s="25"/>
+      <c r="AM18" s="26"/>
     </row>
-    <row r="19" s="2" customFormat="1" ht="13.2" spans="1:33">
-      <c r="A19" s="24" t="s">
+    <row r="19" s="2" customFormat="1" ht="13.2"/>
+    <row r="20" s="2" customFormat="1" ht="13.2" spans="36:37">
+      <c r="AJ20" s="25"/>
+      <c r="AK20" s="44"/>
+    </row>
+    <row r="21" s="3" customFormat="1" spans="35:37">
+      <c r="AI21" s="45"/>
+      <c r="AJ21" s="46"/>
+      <c r="AK21" s="32"/>
+    </row>
+    <row r="22" spans="1:33">
+      <c r="A22" s="23"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23"/>
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23"/>
+      <c r="W22" s="23"/>
+      <c r="X22" s="23"/>
+      <c r="Y22" s="23"/>
+      <c r="Z22" s="23"/>
+      <c r="AA22" s="23"/>
+      <c r="AB22" s="23"/>
+      <c r="AC22" s="23"/>
+      <c r="AD22" s="23"/>
+      <c r="AE22" s="40"/>
+      <c r="AF22" s="40"/>
+      <c r="AG22" s="23"/>
+    </row>
+    <row r="23" spans="1:34">
+      <c r="A23" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="25"/>
-      <c r="C19" s="26" t="s">
+      <c r="B23" s="24"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="25"/>
+    </row>
+    <row r="24" spans="1:34">
+      <c r="A24" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="26"/>
-      <c r="G19" s="26"/>
-      <c r="H19" s="26"/>
-      <c r="I19" s="26"/>
-      <c r="J19" s="26"/>
-      <c r="K19" s="26"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="26"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="25" t="s">
+      <c r="B24" s="25"/>
+      <c r="C24" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="25"/>
-      <c r="R19" s="27" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-      <c r="V19" s="25"/>
-      <c r="W19" s="25" t="s">
+      <c r="P24" s="2"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="X19" s="25"/>
-      <c r="Y19" s="25"/>
-      <c r="Z19" s="25" t="s">
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="AA19" s="25"/>
-      <c r="AB19" s="25"/>
-      <c r="AD19" s="25"/>
-      <c r="AE19" s="25"/>
-      <c r="AF19" s="25" t="s">
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="AG19" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH24" s="25"/>
     </row>
-    <row r="20" s="2" customFormat="1" ht="13.2" spans="1:36">
-      <c r="A20" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25" t="s">
+    <row r="25" spans="1:34">
+      <c r="A25" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26" t="s">
+      <c r="B25" s="25"/>
+      <c r="C25" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-      <c r="R20" s="25" t="s">
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
-      <c r="V20" s="25"/>
-      <c r="W20" s="25" t="s">
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="X20" s="25"/>
-      <c r="Y20" s="25"/>
-      <c r="Z20" s="25" t="s">
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="AA20" s="25"/>
-      <c r="AB20" s="25"/>
-      <c r="AD20" s="25"/>
-      <c r="AE20" s="25"/>
-      <c r="AF20" s="25"/>
-      <c r="AG20" s="25"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="25"/>
-      <c r="AJ20" s="46"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="25"/>
     </row>
-    <row r="21" s="3" customFormat="1" spans="1:36">
-      <c r="A21" s="27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="3" t="s">
+    <row r="26" spans="1:34">
+      <c r="A26" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="M21" s="33"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="26" t="s">
+      <c r="B26" s="27"/>
+      <c r="C26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="25" t="s">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="27"/>
-      <c r="W21" s="27"/>
-      <c r="X21" s="27"/>
-      <c r="Y21" s="27"/>
-      <c r="Z21" s="27"/>
-      <c r="AA21" s="27"/>
-      <c r="AB21" s="27"/>
-      <c r="AC21" s="27"/>
-      <c r="AD21" s="27"/>
-      <c r="AE21" s="27"/>
-      <c r="AF21" s="27"/>
-      <c r="AG21" s="27"/>
-      <c r="AH21" s="47"/>
-      <c r="AI21" s="48"/>
-      <c r="AJ21" s="33"/>
-    </row>
-    <row r="22" spans="1:32">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
-      <c r="L22" s="28"/>
-      <c r="M22" s="28"/>
-      <c r="N22" s="28"/>
-      <c r="O22" s="28"/>
-      <c r="P22" s="28"/>
-      <c r="Q22" s="28"/>
-      <c r="R22" s="28"/>
-      <c r="S22" s="28"/>
-      <c r="T22" s="28"/>
-      <c r="U22" s="28"/>
-      <c r="V22" s="28"/>
-      <c r="W22" s="28"/>
-      <c r="X22" s="28"/>
-      <c r="Y22" s="28"/>
-      <c r="Z22" s="28"/>
-      <c r="AA22" s="28"/>
-      <c r="AB22" s="28"/>
-      <c r="AC22" s="28"/>
-      <c r="AD22" s="44"/>
-      <c r="AE22" s="44"/>
-      <c r="AF22" s="28"/>
-    </row>
-    <row r="23" spans="1:32">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
-      <c r="AA23" s="28"/>
-      <c r="AB23" s="28"/>
-      <c r="AC23" s="28"/>
-      <c r="AD23" s="28"/>
-      <c r="AE23" s="28"/>
-      <c r="AF23" s="28"/>
-    </row>
-    <row r="24" spans="1:32">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="28"/>
-      <c r="P24" s="28"/>
-      <c r="Q24" s="28"/>
-      <c r="R24" s="28"/>
-      <c r="S24" s="28"/>
-      <c r="T24" s="28"/>
-      <c r="U24" s="28"/>
-      <c r="V24" s="28"/>
-      <c r="W24" s="28"/>
-      <c r="X24" s="28"/>
-      <c r="Y24" s="28"/>
-      <c r="Z24" s="28"/>
-      <c r="AA24" s="28"/>
-      <c r="AB24" s="28"/>
-      <c r="AC24" s="28"/>
-      <c r="AD24" s="28"/>
-      <c r="AE24" s="28"/>
-      <c r="AF24" s="28"/>
+      <c r="P26" s="27"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="S26" s="27"/>
+      <c r="T26" s="27"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="27"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
+      <c r="Y26" s="27"/>
+      <c r="Z26" s="27"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="27"/>
+      <c r="AC26" s="27"/>
+      <c r="AD26" s="27"/>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="27"/>
+      <c r="AG26" s="27"/>
+      <c r="AH26" s="27"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A2:AF2"/>
-    <mergeCell ref="A3:AF3"/>
-    <mergeCell ref="U4:AF4"/>
-    <mergeCell ref="U5:AF5"/>
-    <mergeCell ref="U6:AF6"/>
+  <mergeCells count="39">
+    <mergeCell ref="A2:AG2"/>
+    <mergeCell ref="A3:AG3"/>
+    <mergeCell ref="U4:AG4"/>
+    <mergeCell ref="U5:AG5"/>
+    <mergeCell ref="U6:AG6"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="J7:L7"/>
@@ -2571,8 +2562,9 @@
     <mergeCell ref="M8:M9"/>
     <mergeCell ref="AC8:AC9"/>
     <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE11"/>
+    <mergeCell ref="AE7:AE9"/>
     <mergeCell ref="AF7:AF11"/>
+    <mergeCell ref="AG7:AG11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.15748031496063" header="0" footer="0"/>
